--- a/docs/resources/Mappings_testCohort.xlsx
+++ b/docs/resources/Mappings_testCohort.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brend\Molgenis\repos\molgenis-emx2\docs\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HijmansBS\Molgenis\repos\molgenis-emx2\docs\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5D43EBB-7961-4D55-888B-335AA8E4926F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F8B54F-A1E2-466C-810E-5DEA98310671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19395" windowHeight="12195" activeTab="1" xr2:uid="{F86F0FFA-F849-435E-8F15-A7532F91F404}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{F86F0FFA-F849-435E-8F15-A7532F91F404}"/>
   </bookViews>
   <sheets>
-    <sheet name="Dataset mappings" sheetId="1" r:id="rId1"/>
+    <sheet name="Table mappings" sheetId="1" r:id="rId1"/>
     <sheet name="Variable mappings" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -63,13 +63,7 @@
     <t>order</t>
   </si>
   <si>
-    <t>target dataset</t>
-  </si>
-  <si>
     <t>target</t>
-  </si>
-  <si>
-    <t>source dataset</t>
   </si>
   <si>
     <t>source</t>
@@ -240,12 +234,6 @@
     <t>target variable</t>
   </si>
   <si>
-    <t>source variables other datasets.name</t>
-  </si>
-  <si>
-    <t>source variables other datasets.dataset</t>
-  </si>
-  <si>
     <t>source variables</t>
   </si>
   <si>
@@ -256,6 +244,18 @@
   </si>
   <si>
     <t>length_</t>
+  </si>
+  <si>
+    <t>source table</t>
+  </si>
+  <si>
+    <t>target table</t>
+  </si>
+  <si>
+    <t>source variables other tables.table</t>
+  </si>
+  <si>
+    <t>source variables other tables.name</t>
   </si>
 </sst>
 </file>
@@ -628,29 +628,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{567CEEA9-5F71-49AF-BB90-1AD5AB1FBBB8}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.86328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.46484375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.86328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="C1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="E1" t="s">
         <v>7</v>
@@ -662,7 +662,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -676,7 +676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -698,53 +698,53 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F58A07B1-53BA-40D4-9576-224AC8829486}">
   <dimension ref="A1:M16"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.06640625" customWidth="1"/>
-    <col min="5" max="5" width="32.19921875" customWidth="1"/>
-    <col min="6" max="6" width="7.86328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.46484375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.53125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.1328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="57.73046875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="79.1328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.1328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.109375" customWidth="1"/>
+    <col min="5" max="5" width="32.21875" customWidth="1"/>
+    <col min="6" max="6" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="57.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="79.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="C1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1" t="s">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="H1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K1" t="s">
         <v>6</v>
@@ -753,10 +753,10 @@
         <v>5</v>
       </c>
       <c r="M1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -764,7 +764,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F2" t="s">
         <v>1</v>
@@ -773,19 +773,19 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -793,7 +793,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F3" t="s">
         <v>1</v>
@@ -802,19 +802,19 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -822,7 +822,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F4" t="s">
         <v>1</v>
@@ -831,364 +831,364 @@
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" t="s">
+        <v>11</v>
+      </c>
+      <c r="J7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K7" t="s">
+        <v>44</v>
+      </c>
+      <c r="L7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>0</v>
+      </c>
+      <c r="H10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s">
+        <v>67</v>
+      </c>
+      <c r="F14" t="s">
+        <v>1</v>
+      </c>
+      <c r="G14" t="s">
+        <v>0</v>
+      </c>
+      <c r="H14" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" t="s">
+        <v>65</v>
+      </c>
+      <c r="J14" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" t="s">
+        <v>1</v>
+      </c>
+      <c r="G15" t="s">
         <v>20</v>
       </c>
-      <c r="J4" t="s">
+      <c r="H15" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" t="s">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
+        <v>0</v>
+      </c>
+      <c r="H16" t="s">
         <v>12</v>
       </c>
-      <c r="L4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F5" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" t="s">
-        <v>0</v>
-      </c>
-      <c r="H5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" t="s">
-        <v>0</v>
-      </c>
-      <c r="H6" t="s">
-        <v>50</v>
-      </c>
-      <c r="I6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H7" t="s">
-        <v>47</v>
-      </c>
-      <c r="I7" t="s">
-        <v>13</v>
-      </c>
-      <c r="J7" t="s">
-        <v>12</v>
-      </c>
-      <c r="K7" t="s">
-        <v>46</v>
-      </c>
-      <c r="L7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" t="s">
-        <v>0</v>
-      </c>
-      <c r="H8" t="s">
-        <v>33</v>
-      </c>
-      <c r="I8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" t="s">
-        <v>1</v>
-      </c>
-      <c r="G9" t="s">
-        <v>0</v>
-      </c>
-      <c r="H9" t="s">
-        <v>33</v>
-      </c>
-      <c r="I9" t="s">
-        <v>31</v>
-      </c>
-      <c r="J9" t="s">
-        <v>24</v>
-      </c>
-      <c r="L9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" t="s">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>0</v>
-      </c>
-      <c r="H10" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" t="s">
-        <v>30</v>
-      </c>
-      <c r="J10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" t="s">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
-        <v>0</v>
-      </c>
-      <c r="H11" t="s">
-        <v>33</v>
-      </c>
-      <c r="I11" t="s">
-        <v>29</v>
-      </c>
-      <c r="J11" t="s">
-        <v>24</v>
-      </c>
-      <c r="L11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12" t="s">
-        <v>1</v>
-      </c>
-      <c r="G12" t="s">
-        <v>0</v>
-      </c>
-      <c r="H12" t="s">
-        <v>33</v>
-      </c>
-      <c r="I12" t="s">
-        <v>28</v>
-      </c>
-      <c r="J12" t="s">
-        <v>24</v>
-      </c>
-      <c r="L12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" t="s">
-        <v>34</v>
-      </c>
-      <c r="F13" t="s">
-        <v>1</v>
-      </c>
-      <c r="G13" t="s">
-        <v>0</v>
-      </c>
-      <c r="H13" t="s">
-        <v>33</v>
-      </c>
-      <c r="I13" t="s">
-        <v>25</v>
-      </c>
-      <c r="J13" t="s">
-        <v>24</v>
-      </c>
-      <c r="L13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" t="s">
-        <v>71</v>
-      </c>
-      <c r="F14" t="s">
-        <v>1</v>
-      </c>
-      <c r="G14" t="s">
-        <v>0</v>
-      </c>
-      <c r="H14" t="s">
-        <v>26</v>
-      </c>
-      <c r="I14" t="s">
-        <v>69</v>
-      </c>
-      <c r="J14" t="s">
-        <v>24</v>
-      </c>
-      <c r="L14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" t="s">
-        <v>23</v>
-      </c>
-      <c r="F15" t="s">
-        <v>1</v>
-      </c>
-      <c r="G15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H15" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15" t="s">
-        <v>20</v>
-      </c>
-      <c r="J15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" t="s">
-        <v>1</v>
-      </c>
-      <c r="G16" t="s">
-        <v>0</v>
-      </c>
-      <c r="H16" t="s">
-        <v>14</v>
-      </c>
       <c r="I16" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J16" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
